--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
@@ -464,12 +464,12 @@
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - paddle</t>
+          <t>Possible duplicate lines - paddle</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap - abbyy</t>
+          <t>Possible duplicate lines - abbyy</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
@@ -1003,7 +1003,7 @@
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>duplicate/tile overlap issue count</t>
+          <t>Possible duplicate lines issue count</t>
         </is>
       </c>
       <c r="B7" s="1" t="inlineStr">

--- a/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
+++ b/3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl/test-results/page-level-excels/oocihm.N_00138_18940629/oocihm.N_00138_18940629.4.xlsx
@@ -423,7 +423,7 @@
     <col width="60" customWidth="1" min="2" max="2"/>
     <col width="60" customWidth="1" min="3" max="3"/>
     <col width="60" customWidth="1" min="4" max="4"/>
-    <col width="32" customWidth="1" min="5" max="5"/>
+    <col width="34" customWidth="1" min="5" max="5"/>
     <col width="60" customWidth="1" min="6" max="6"/>
     <col width="35" customWidth="1" min="7" max="7"/>
     <col width="60" customWidth="1" min="8" max="8"/>
@@ -431,7 +431,7 @@
     <col width="60" customWidth="1" min="10" max="10"/>
     <col width="60" customWidth="1" min="11" max="11"/>
     <col width="32" customWidth="1" min="12" max="12"/>
-    <col width="31" customWidth="1" min="13" max="13"/>
+    <col width="60" customWidth="1" min="13" max="13"/>
     <col width="60" customWidth="1" min="14" max="14"/>
     <col width="60" customWidth="1" min="15" max="15"/>
     <col width="60" customWidth="1" min="16" max="16"/>
@@ -581,12 +581,12 @@
       </c>
       <c r="B2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\preprocessing-tiling_3x1_dp+paddleocr+vl+clean\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
         </is>
       </c>
       <c r="C2" s="1" t="inlineStr">
         <is>
-          <t>C:\Users\BrittnyLapierre\Documents\OCR-Evaluations\3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
+          <t>3-multi-document-abbyy-vs-tiled3x1+docparse-paddleocr-paddlevl\test-data\abbyy\oocihm.N_00138_18940629\oocihm.N_00138_18940629.4.txt</t>
         </is>
       </c>
       <c r="D2" s="1" t="inlineStr">
@@ -613,16 +613,20 @@
       </c>
       <c r="J2" s="1" t="inlineStr">
         <is>
-          <t>L11: stray/suspicious non-ASCII glyph(s): U+00A9 COPYRIGHT SIGN :: gÃ©nÃ©ral</t>
+          <t>L273: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="K2" s="1" t="inlineStr">
         <is>
-          <t>L47: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: he didn't care whether Her Majestyâ€™s</t>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES, FRIDAY, JUNE 29,1894.</t>
         </is>
       </c>
       <c r="L2" s="1" t="inlineStr"/>
-      <c r="M2" s="1" t="inlineStr"/>
+      <c r="M2" s="1" t="inlineStr">
+        <is>
+          <t>L1: BOM/control character at start of file | stray/suspicious non-ASCII glyph(s): U+FEFF ZERO WIDTH NO-BREAK SPACE :: [BOM]HAMILTON EVENING TIMES, FRIDAY, JUNE 29,1894.</t>
+        </is>
+      </c>
       <c r="N2" s="1" t="inlineStr">
         <is>
           <t>L10: isolated marker/symbol line :: a</t>
@@ -650,7 +654,7 @@
       </c>
       <c r="S2" s="1" t="inlineStr">
         <is>
-          <t>L1070: line starts with digit/letter garbage token | suspicious token(s): 2From (letter/digit mix) :: 2From $1.00 to $2.50.</t>
+          <t>L735: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • done in the first instance, repairs will</t>
         </is>
       </c>
       <c r="T2" s="1" t="inlineStr"/>
@@ -681,7 +685,7 @@
       </c>
       <c r="C3" s="1" t="inlineStr">
         <is>
-          <t>1217</t>
+          <t>923</t>
         </is>
       </c>
       <c r="D3" s="1" t="inlineStr">
@@ -708,12 +712,12 @@
       </c>
       <c r="J3" s="1" t="inlineStr">
         <is>
-          <t>L168: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: called â€œorder. Hardie refused to</t>
+          <t>L511: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: G. Mitchell, Jenetta McNeilly ， Caroline</t>
         </is>
       </c>
       <c r="K3" s="1" t="inlineStr">
         <is>
-          <t>L174: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Wentworth School â€” Girls : Maggie</t>
+          <t>L735: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • done in the first instance, repairs will</t>
         </is>
       </c>
       <c r="L3" s="1" t="inlineStr"/>
@@ -739,7 +743,11 @@
         </is>
       </c>
       <c r="R3" s="1" t="inlineStr"/>
-      <c r="S3" s="1" t="inlineStr"/>
+      <c r="S3" s="1" t="inlineStr">
+        <is>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Works. It is stipulated that the stone</t>
+        </is>
+      </c>
       <c r="T3" s="1" t="inlineStr"/>
       <c r="U3" s="1" t="inlineStr"/>
       <c r="V3" s="1" t="inlineStr">
@@ -791,12 +799,12 @@
       </c>
       <c r="J4" s="1" t="inlineStr">
         <is>
-          <t>L422: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: gullible â€œheirsâ€� spent '$ 7, 600 good</t>
+          <t>L522: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: struction: John M. I. Byrens ， Nellie Wey.</t>
         </is>
       </c>
       <c r="K4" s="1" t="inlineStr">
         <is>
-          <t>L185: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Boysâ€™ Home- W. Hartzmark.</t>
+          <t>L975: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • Works. It is stipulated that the stone</t>
         </is>
       </c>
       <c r="L4" s="1" t="inlineStr"/>
@@ -822,7 +830,11 @@
         </is>
       </c>
       <c r="R4" s="1" t="inlineStr"/>
-      <c r="S4" s="1" t="inlineStr"/>
+      <c r="S4" s="1" t="inlineStr">
+        <is>
+          <t>L1070: line starts with digit/letter garbage token | suspicious token(s): 2From (letter/digit mix) :: 2From $1.00 to $2.50.</t>
+        </is>
+      </c>
       <c r="T4" s="1" t="inlineStr"/>
       <c r="U4" s="1" t="inlineStr"/>
       <c r="V4" s="1" t="inlineStr">
@@ -842,12 +854,12 @@
       </c>
       <c r="B5" s="1" t="inlineStr">
         <is>
-          <t>95</t>
+          <t>92</t>
         </is>
       </c>
       <c r="C5" s="1" t="inlineStr">
         <is>
-          <t>105</t>
+          <t>75</t>
         </is>
       </c>
       <c r="D5" s="1" t="inlineStr">
@@ -874,19 +886,19 @@
       </c>
       <c r="J5" s="1" t="inlineStr">
         <is>
-          <t>L423: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+FFFD REPLACEMENT CHARACTER :: â€œheirsâ€�</t>
+          <t>L525: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): MeNeflyOttilieE (odd internal casing) :: Jenetta MeNeflyOttilieE. Palm ， Dora</t>
         </is>
       </c>
       <c r="K5" s="1" t="inlineStr">
         <is>
-          <t>L191: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: architectureâ€”John M. Byrens.</t>
+          <t>L1208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • up the system.</t>
         </is>
       </c>
       <c r="L5" s="1" t="inlineStr"/>
       <c r="M5" s="1" t="inlineStr"/>
       <c r="N5" s="1" t="inlineStr">
         <is>
-          <t>L274: isolated marker/symbol line :: Ï‰</t>
+          <t>L273: stray/suspicious non-ASCII glyph(s): U+5FC3 CJK UNIFIED IDEOGRAPH-5FC3 | isolated marker/symbol line :: 心</t>
         </is>
       </c>
       <c r="O5" s="1" t="inlineStr">
@@ -905,12 +917,16 @@
         </is>
       </c>
       <c r="R5" s="1" t="inlineStr"/>
-      <c r="S5" s="1" t="inlineStr"/>
+      <c r="S5" s="1" t="inlineStr">
+        <is>
+          <t>L1208: stray/suspicious non-ASCII glyph(s): U+2022 BULLET | line starts with punctuation glued to text :: • up the system.</t>
+        </is>
+      </c>
       <c r="T5" s="1" t="inlineStr"/>
       <c r="U5" s="1" t="inlineStr"/>
       <c r="V5" s="1" t="inlineStr">
         <is>
-          <t>L808: suspicious token(s): NormaLuxton (odd internal casing) | abbreviation/spacing may be garbled :: Leckenbyï¼ŒChas.F.A.Locke, NormaLuxton,</t>
+          <t>L808: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): NormaLuxton (odd internal casing) | abbreviation/spacing may be garbled :: Leckenby，Chas.F.A.Locke, NormaLuxton,</t>
         </is>
       </c>
       <c r="W5" s="1" t="inlineStr"/>
@@ -941,7 +957,7 @@
       <c r="E6" s="1" t="inlineStr"/>
       <c r="F6" s="1" t="inlineStr">
         <is>
-          <t>L622: candidate OCR token mismatch vs other OCR: "Worka" vs "Works" :: Worka. It is stipulated that the stone</t>
+          <t>L740: candidate OCR token mismatch vs other OCR: "halis" vs "halls" :: The very halis of state they'll scrub,</t>
         </is>
       </c>
       <c r="G6" s="1" t="inlineStr"/>
@@ -957,19 +973,15 @@
       </c>
       <c r="J6" s="1" t="inlineStr">
         <is>
-          <t>L428: stray/suspicious non-ASCII glyph(s): U+FFFD REPLACEMENT CHARACTER :: rope, has ended with the conviction Ï� f</t>
-        </is>
-      </c>
-      <c r="K6" s="1" t="inlineStr">
-        <is>
-          <t>L212: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Extra Advanced Course â€” Painting oil</t>
-        </is>
-      </c>
+          <t>L545: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: Mitchell ， Frank Hl. Nairn ， Ottilie Palm,</t>
+        </is>
+      </c>
+      <c r="K6" s="1" t="inlineStr"/>
       <c r="L6" s="1" t="inlineStr"/>
       <c r="M6" s="1" t="inlineStr"/>
       <c r="N6" s="1" t="inlineStr">
         <is>
-          <t>L297: isolated marker/symbol line :: A</t>
+          <t>L274: isolated marker/symbol line :: ω</t>
         </is>
       </c>
       <c r="O6" s="1" t="inlineStr">
@@ -1024,7 +1036,7 @@
       <c r="E7" s="1" t="inlineStr"/>
       <c r="F7" s="1" t="inlineStr">
         <is>
-          <t>L635: candidate OCR token mismatch vs other OCR: "scurbing" vs "curbing" :: scurbing, even if the cutter has begun on</t>
+          <t>L758: candidate OCR token mismatch vs other OCR: "guest" vs "quest" :: Alone upon her solemn guest,</t>
         </is>
       </c>
       <c r="G7" s="1" t="inlineStr"/>
@@ -1040,24 +1052,20 @@
       </c>
       <c r="J7" s="1" t="inlineStr">
         <is>
-          <t>L432: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: of the â€œnext of kin " advertisers, who</t>
-        </is>
-      </c>
-      <c r="K7" s="1" t="inlineStr">
-        <is>
-          <t>L225: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Mechanical Art Courseâ€”Industrial de-</t>
-        </is>
-      </c>
+          <t>L686: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K7" s="1" t="inlineStr"/>
       <c r="L7" s="1" t="inlineStr"/>
       <c r="M7" s="1" t="inlineStr"/>
       <c r="N7" s="1" t="inlineStr">
         <is>
-          <t>L298: isolated marker/symbol line :: n</t>
+          <t>L297: isolated marker/symbol line :: A</t>
         </is>
       </c>
       <c r="O7" s="1" t="inlineStr">
         <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
+          <t>L665: isolated marker/symbol line :: —</t>
         </is>
       </c>
       <c r="P7" s="1" t="inlineStr">
@@ -1087,7 +1095,7 @@
       </c>
       <c r="B8" s="1" t="inlineStr">
         <is>
-          <t>7</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C8" s="1" t="inlineStr">
@@ -1097,11 +1105,7 @@
       </c>
       <c r="D8" s="1" t="inlineStr"/>
       <c r="E8" s="1" t="inlineStr"/>
-      <c r="F8" s="1" t="inlineStr">
-        <is>
-          <t>L705: candidate OCR token mismatch vs other OCR: "Frencl" vs "French" :: "Frencl people there would be no Can-</t>
-        </is>
-      </c>
+      <c r="F8" s="1" t="inlineStr"/>
       <c r="G8" s="1" t="inlineStr"/>
       <c r="H8" s="1" t="inlineStr">
         <is>
@@ -1115,19 +1119,15 @@
       </c>
       <c r="J8" s="1" t="inlineStr">
         <is>
-          <t>L527: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Advanced Art Course â€” Shading from.</t>
-        </is>
-      </c>
-      <c r="K8" s="1" t="inlineStr">
-        <is>
-          <t>L244: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Advanced Art Course â€” Shading from,</t>
-        </is>
-      </c>
+          <t>L687: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
+        </is>
+      </c>
+      <c r="K8" s="1" t="inlineStr"/>
       <c r="L8" s="1" t="inlineStr"/>
       <c r="M8" s="1" t="inlineStr"/>
       <c r="N8" s="1" t="inlineStr">
         <is>
-          <t>L299: isolated marker/symbol line :: 4</t>
+          <t>L298: isolated marker/symbol line :: n</t>
         </is>
       </c>
       <c r="O8" s="1" t="inlineStr">
@@ -1177,24 +1177,20 @@
       </c>
       <c r="I9" s="1" t="inlineStr">
         <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 15c (letter/digit mix) :: 20 doz. Ladiesâ€™ Cotton Drawers 15c, worth 506.</t>
+          <t>L351: suspicious token(s): 15c (letter/digit mix) :: 20 doz. Ladies’ Cotton Drawers 15c, worth 506.</t>
         </is>
       </c>
       <c r="J9" s="1" t="inlineStr">
         <is>
-          <t>L686: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K9" s="1" t="inlineStr">
-        <is>
-          <t>L319: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: " It canâ€™t be true," she said, "that</t>
-        </is>
-      </c>
+          <t>L808: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): NormaLuxton (odd internal casing) | abbreviation/spacing may be garbled :: Leckenby，Chas.F.A.Locke, NormaLuxton,</t>
+        </is>
+      </c>
+      <c r="K9" s="1" t="inlineStr"/>
       <c r="L9" s="1" t="inlineStr"/>
       <c r="M9" s="1" t="inlineStr"/>
       <c r="N9" s="1" t="inlineStr">
         <is>
-          <t>L301: isolated marker/symbol line :: S</t>
+          <t>L299: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O9" s="1" t="inlineStr">
@@ -1225,12 +1221,12 @@
       </c>
       <c r="B10" s="1" t="inlineStr">
         <is>
-          <t>11</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C10" s="1" t="inlineStr">
         <is>
-          <t>36</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D10" s="1" t="inlineStr"/>
@@ -1249,19 +1245,15 @@
       </c>
       <c r="J10" s="1" t="inlineStr">
         <is>
-          <t>L687: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
-        </is>
-      </c>
-      <c r="K10" s="1" t="inlineStr">
-        <is>
-          <t>L351: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN | suspicious token(s): 15c (letter/digit mix) :: 20 doz. Ladiesâ€™ Cotton Drawers 15c, worth 506.</t>
-        </is>
-      </c>
+          <t>L827: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA :: bell, Matthew Garvin，Herbert Mason,</t>
+        </is>
+      </c>
+      <c r="K10" s="1" t="inlineStr"/>
       <c r="L10" s="1" t="inlineStr"/>
       <c r="M10" s="1" t="inlineStr"/>
       <c r="N10" s="1" t="inlineStr">
         <is>
-          <t>L561: isolated marker/symbol line :: 25</t>
+          <t>L301: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O10" s="1" t="inlineStr">
@@ -1293,7 +1285,7 @@
       </c>
       <c r="C11" s="1" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>1</t>
         </is>
       </c>
       <c r="D11" s="1" t="inlineStr"/>
@@ -1312,19 +1304,15 @@
       </c>
       <c r="J11" s="1" t="inlineStr">
         <is>
-          <t>L943: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K11" s="1" t="inlineStr">
-        <is>
-          <t>L374: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: Pursesâ€”a large purchase of fine new goods.</t>
-        </is>
-      </c>
+          <t>L832: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA, U+FF1B FULLWIDTH SEMICOLON | suspicious token(s): MnrielHills (odd internal casing) :: vin, Fannie Gunn ， MnrielHills ； Mabel</t>
+        </is>
+      </c>
+      <c r="K11" s="1" t="inlineStr"/>
       <c r="L11" s="1" t="inlineStr"/>
       <c r="M11" s="1" t="inlineStr"/>
       <c r="N11" s="1" t="inlineStr">
         <is>
-          <t>L615: isolated marker/symbol line :: 2</t>
+          <t>L561: isolated marker/symbol line :: 25</t>
         </is>
       </c>
       <c r="O11" s="1" t="inlineStr">
@@ -1351,7 +1339,7 @@
       </c>
       <c r="B12" s="1" t="inlineStr">
         <is>
-          <t>30</t>
+          <t>31</t>
         </is>
       </c>
       <c r="C12" s="1" t="inlineStr">
@@ -1375,19 +1363,15 @@
       </c>
       <c r="J12" s="1" t="inlineStr">
         <is>
-          <t>L945: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
-        </is>
-      </c>
-      <c r="K12" s="1" t="inlineStr">
-        <is>
-          <t>L437: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: . old question of taxationâ€”whether</t>
-        </is>
-      </c>
+          <t>L943: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K12" s="1" t="inlineStr"/>
       <c r="L12" s="1" t="inlineStr"/>
       <c r="M12" s="1" t="inlineStr"/>
       <c r="N12" s="1" t="inlineStr">
         <is>
-          <t>L674: isolated marker/symbol line :: 2</t>
+          <t>L615: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O12" s="1" t="inlineStr">
@@ -1436,17 +1420,17 @@
           <t>L359: suspicious token(s): 1c (letter/digit mix) :: Ladies' Colored Linen Collars 1c.</t>
         </is>
       </c>
-      <c r="J13" s="1" t="inlineStr"/>
-      <c r="K13" s="1" t="inlineStr">
-        <is>
-          <t>L525: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Fosterâ€™s latest tariff bill, and it will be</t>
-        </is>
-      </c>
+      <c r="J13" s="1" t="inlineStr">
+        <is>
+          <t>L945: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
+        </is>
+      </c>
+      <c r="K13" s="1" t="inlineStr"/>
       <c r="L13" s="1" t="inlineStr"/>
       <c r="M13" s="1" t="inlineStr"/>
       <c r="N13" s="1" t="inlineStr">
         <is>
-          <t>L675: isolated marker/symbol line :: 4</t>
+          <t>L674: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O13" s="1" t="inlineStr">
@@ -1478,7 +1462,7 @@
       </c>
       <c r="C14" s="1" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>4</t>
         </is>
       </c>
       <c r="D14" s="1" t="inlineStr"/>
@@ -1496,16 +1480,12 @@
         </is>
       </c>
       <c r="J14" s="1" t="inlineStr"/>
-      <c r="K14" s="1" t="inlineStr">
-        <is>
-          <t>L665: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: â€”</t>
-        </is>
-      </c>
+      <c r="K14" s="1" t="inlineStr"/>
       <c r="L14" s="1" t="inlineStr"/>
       <c r="M14" s="1" t="inlineStr"/>
       <c r="N14" s="1" t="inlineStr">
         <is>
-          <t>L676: isolated marker/symbol line :: 2</t>
+          <t>L675: isolated marker/symbol line :: 4</t>
         </is>
       </c>
       <c r="O14" s="1" t="inlineStr">
@@ -1555,16 +1535,12 @@
         </is>
       </c>
       <c r="J15" s="1" t="inlineStr"/>
-      <c r="K15" s="1" t="inlineStr">
-        <is>
-          <t>L720: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: rontoâ€™s asphalt pavement, which he</t>
-        </is>
-      </c>
+      <c r="K15" s="1" t="inlineStr"/>
       <c r="L15" s="1" t="inlineStr"/>
       <c r="M15" s="1" t="inlineStr"/>
       <c r="N15" s="1" t="inlineStr">
         <is>
-          <t>L677: isolated marker/symbol line :: D</t>
+          <t>L676: isolated marker/symbol line :: 2</t>
         </is>
       </c>
       <c r="O15" s="1" t="inlineStr">
@@ -1605,7 +1581,7 @@
       <c r="G16" s="1" t="inlineStr"/>
       <c r="H16" s="1" t="inlineStr">
         <is>
-          <t>L525: suspicious token(s): MeNeflyOttilieE (odd internal casing) :: Jenetta MeNeflyOttilieE. Palm ï¼Œ Dora</t>
+          <t>L525: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): MeNeflyOttilieE (odd internal casing) :: Jenetta MeNeflyOttilieE. Palm ， Dora</t>
         </is>
       </c>
       <c r="I16" s="1" t="inlineStr">
@@ -1614,16 +1590,12 @@
         </is>
       </c>
       <c r="J16" s="1" t="inlineStr"/>
-      <c r="K16" s="1" t="inlineStr">
-        <is>
-          <t>L735: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ done in the first instance, repairs will</t>
-        </is>
-      </c>
+      <c r="K16" s="1" t="inlineStr"/>
       <c r="L16" s="1" t="inlineStr"/>
       <c r="M16" s="1" t="inlineStr"/>
       <c r="N16" s="1" t="inlineStr">
         <is>
-          <t>L686: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L677: isolated marker/symbol line :: D</t>
         </is>
       </c>
       <c r="O16" s="1" t="inlineStr">
@@ -1673,16 +1645,12 @@
         </is>
       </c>
       <c r="J17" s="1" t="inlineStr"/>
-      <c r="K17" s="1" t="inlineStr">
-        <is>
-          <t>L819: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Poem read at Miss Willardâ€™s welcome</t>
-        </is>
-      </c>
+      <c r="K17" s="1" t="inlineStr"/>
       <c r="L17" s="1" t="inlineStr"/>
       <c r="M17" s="1" t="inlineStr"/>
       <c r="N17" s="1" t="inlineStr">
         <is>
-          <t>L687: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN | isolated marker/symbol line :: ã€‚</t>
+          <t>L686: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O17" s="1" t="inlineStr">
@@ -1720,16 +1688,12 @@
         </is>
       </c>
       <c r="J18" s="1" t="inlineStr"/>
-      <c r="K18" s="1" t="inlineStr">
-        <is>
-          <t>L823: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Thereâ€™s but one sphere for man and</t>
-        </is>
-      </c>
+      <c r="K18" s="1" t="inlineStr"/>
       <c r="L18" s="1" t="inlineStr"/>
       <c r="M18" s="1" t="inlineStr"/>
       <c r="N18" s="1" t="inlineStr">
         <is>
-          <t>L688: isolated marker/symbol line :: 0</t>
+          <t>L687: stray/suspicious non-ASCII glyph(s): U+3002 IDEOGRAPHIC FULL STOP | isolated marker/symbol line :: 。</t>
         </is>
       </c>
       <c r="O18" s="1" t="inlineStr">
@@ -1767,16 +1731,12 @@
         </is>
       </c>
       <c r="J19" s="1" t="inlineStr"/>
-      <c r="K19" s="1" t="inlineStr">
-        <is>
-          <t>L838: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: To Hades heâ€™ll be soon remanded.</t>
-        </is>
-      </c>
+      <c r="K19" s="1" t="inlineStr"/>
       <c r="L19" s="1" t="inlineStr"/>
       <c r="M19" s="1" t="inlineStr"/>
       <c r="N19" s="1" t="inlineStr">
         <is>
-          <t>L790: isolated marker/symbol line :: &gt;</t>
+          <t>L688: isolated marker/symbol line :: 0</t>
         </is>
       </c>
       <c r="O19" s="1" t="inlineStr">
@@ -1814,16 +1774,12 @@
         </is>
       </c>
       <c r="J20" s="1" t="inlineStr"/>
-      <c r="K20" s="1" t="inlineStr">
-        <is>
-          <t>L840: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: And thatâ€™s the case with all his minions:</t>
-        </is>
-      </c>
+      <c r="K20" s="1" t="inlineStr"/>
       <c r="L20" s="1" t="inlineStr"/>
       <c r="M20" s="1" t="inlineStr"/>
       <c r="N20" s="1" t="inlineStr">
         <is>
-          <t>L905: isolated marker/symbol line :: D.</t>
+          <t>L790: isolated marker/symbol line :: &gt;</t>
         </is>
       </c>
       <c r="O20" s="1" t="inlineStr">
@@ -1861,16 +1817,12 @@
         </is>
       </c>
       <c r="J21" s="1" t="inlineStr"/>
-      <c r="K21" s="1" t="inlineStr">
-        <is>
-          <t>L844: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: From dirty politics": theyâ€™ve wielded</t>
-        </is>
-      </c>
+      <c r="K21" s="1" t="inlineStr"/>
       <c r="L21" s="1" t="inlineStr"/>
       <c r="M21" s="1" t="inlineStr"/>
       <c r="N21" s="1" t="inlineStr">
         <is>
-          <t>L920: isolated marker/symbol line :: &lt; 3</t>
+          <t>L905: isolated marker/symbol line :: D.</t>
         </is>
       </c>
       <c r="O21" s="1" t="inlineStr">
@@ -1908,16 +1860,12 @@
         </is>
       </c>
       <c r="J22" s="1" t="inlineStr"/>
-      <c r="K22" s="1" t="inlineStr">
-        <is>
-          <t>L848: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: When, in a hencoopâ€™s safe dominions,</t>
-        </is>
-      </c>
+      <c r="K22" s="1" t="inlineStr"/>
       <c r="L22" s="1" t="inlineStr"/>
       <c r="M22" s="1" t="inlineStr"/>
       <c r="N22" s="1" t="inlineStr">
         <is>
-          <t>L921: isolated marker/symbol line :: N</t>
+          <t>L920: isolated marker/symbol line :: &lt; 3</t>
         </is>
       </c>
       <c r="O22" s="1" t="inlineStr">
@@ -1955,16 +1903,12 @@
         </is>
       </c>
       <c r="J23" s="1" t="inlineStr"/>
-      <c r="K23" s="1" t="inlineStr">
-        <is>
-          <t>L852: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Iâ€™ve not observed the uncaged bird</t>
-        </is>
-      </c>
+      <c r="K23" s="1" t="inlineStr"/>
       <c r="L23" s="1" t="inlineStr"/>
       <c r="M23" s="1" t="inlineStr"/>
       <c r="N23" s="1" t="inlineStr">
         <is>
-          <t>L923: isolated marker/symbol line :: I</t>
+          <t>L921: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O23" s="1" t="inlineStr">
@@ -1993,7 +1937,7 @@
       <c r="G24" s="1" t="inlineStr"/>
       <c r="H24" s="1" t="inlineStr">
         <is>
-          <t>L581: suspicious token(s): 8c (letter/digit mix) :: regular 8c, Saturday 5 Â½ c</t>
+          <t>L581: suspicious token(s): 8c (letter/digit mix) :: regular 8c, Saturday 5 ½ c</t>
         </is>
       </c>
       <c r="I24" s="1" t="inlineStr">
@@ -2002,16 +1946,12 @@
         </is>
       </c>
       <c r="J24" s="1" t="inlineStr"/>
-      <c r="K24" s="1" t="inlineStr">
-        <is>
-          <t>L866: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: In government, and-thereâ€™s the rub!</t>
-        </is>
-      </c>
+      <c r="K24" s="1" t="inlineStr"/>
       <c r="L24" s="1" t="inlineStr"/>
       <c r="M24" s="1" t="inlineStr"/>
       <c r="N24" s="1" t="inlineStr">
         <is>
-          <t>L924: isolated marker/symbol line :: N</t>
+          <t>L923: isolated marker/symbol line :: I</t>
         </is>
       </c>
       <c r="O24" s="1" t="inlineStr">
@@ -2040,7 +1980,7 @@
       <c r="G25" s="1" t="inlineStr"/>
       <c r="H25" s="1" t="inlineStr">
         <is>
-          <t>L588: suspicious token(s): 35c (letter/digit mix) :: 35c, Saturday's price 19 Â½ C.</t>
+          <t>L588: suspicious token(s): 35c (letter/digit mix) :: 35c, Saturday's price 19 ½ C.</t>
         </is>
       </c>
       <c r="I25" s="1" t="inlineStr">
@@ -2049,16 +1989,12 @@
         </is>
       </c>
       <c r="J25" s="1" t="inlineStr"/>
-      <c r="K25" s="1" t="inlineStr">
-        <is>
-          <t>L867: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: The very halls of state theyâ€™ll scrub,</t>
-        </is>
-      </c>
+      <c r="K25" s="1" t="inlineStr"/>
       <c r="L25" s="1" t="inlineStr"/>
       <c r="M25" s="1" t="inlineStr"/>
       <c r="N25" s="1" t="inlineStr">
         <is>
-          <t>L925: isolated marker/symbol line :: G</t>
+          <t>L924: isolated marker/symbol line :: N</t>
         </is>
       </c>
       <c r="O25" s="1" t="inlineStr">
@@ -2096,16 +2032,12 @@
         </is>
       </c>
       <c r="J26" s="1" t="inlineStr"/>
-      <c r="K26" s="1" t="inlineStr">
-        <is>
-          <t>L880: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: And when theyâ€™ve tried it, fact discloses</t>
-        </is>
-      </c>
+      <c r="K26" s="1" t="inlineStr"/>
       <c r="L26" s="1" t="inlineStr"/>
       <c r="M26" s="1" t="inlineStr"/>
       <c r="N26" s="1" t="inlineStr">
         <is>
-          <t>L926: isolated marker/symbol line :: S</t>
+          <t>L925: isolated marker/symbol line :: G</t>
         </is>
       </c>
       <c r="O26" s="1" t="inlineStr">
@@ -2143,16 +2075,12 @@
         </is>
       </c>
       <c r="J27" s="1" t="inlineStr"/>
-      <c r="K27" s="1" t="inlineStr">
-        <is>
-          <t>L882: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: That even election dayâ€™s serene.</t>
-        </is>
-      </c>
+      <c r="K27" s="1" t="inlineStr"/>
       <c r="L27" s="1" t="inlineStr"/>
       <c r="M27" s="1" t="inlineStr"/>
       <c r="N27" s="1" t="inlineStr">
         <is>
-          <t>L941: isolated marker/symbol line :: +</t>
+          <t>L926: isolated marker/symbol line :: S</t>
         </is>
       </c>
       <c r="O27" s="1" t="inlineStr">
@@ -2190,16 +2118,12 @@
         </is>
       </c>
       <c r="J28" s="1" t="inlineStr"/>
-      <c r="K28" s="1" t="inlineStr">
-        <is>
-          <t>L918: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: At freedomâ€™s fount, till, newly fledged,</t>
-        </is>
-      </c>
+      <c r="K28" s="1" t="inlineStr"/>
       <c r="L28" s="1" t="inlineStr"/>
       <c r="M28" s="1" t="inlineStr"/>
       <c r="N28" s="1" t="inlineStr">
         <is>
-          <t>L942: isolated marker/symbol line :: ,</t>
+          <t>L941: isolated marker/symbol line :: +</t>
         </is>
       </c>
       <c r="O28" s="1" t="inlineStr">
@@ -2237,16 +2161,12 @@
         </is>
       </c>
       <c r="J29" s="1" t="inlineStr"/>
-      <c r="K29" s="1" t="inlineStr">
-        <is>
-          <t>L942: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN :: And yetâ€”this woman cannot vote !</t>
-        </is>
-      </c>
+      <c r="K29" s="1" t="inlineStr"/>
       <c r="L29" s="1" t="inlineStr"/>
       <c r="M29" s="1" t="inlineStr"/>
       <c r="N29" s="1" t="inlineStr">
         <is>
-          <t>L943: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L942: isolated marker/symbol line :: ,</t>
         </is>
       </c>
       <c r="O29" s="1" t="inlineStr">
@@ -2284,16 +2204,12 @@
         </is>
       </c>
       <c r="J30" s="1" t="inlineStr"/>
-      <c r="K30" s="1" t="inlineStr">
-        <is>
-          <t>L975: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ Works. It is stipulated that the stone</t>
-        </is>
-      </c>
+      <c r="K30" s="1" t="inlineStr"/>
       <c r="L30" s="1" t="inlineStr"/>
       <c r="M30" s="1" t="inlineStr"/>
       <c r="N30" s="1" t="inlineStr">
         <is>
-          <t>L945: stray/suspicious non-ASCII glyph(s): U+00B8 CEDILLA, U+00AD SOFT HYPHEN | isolated marker/symbol line :: ä¸­</t>
+          <t>L943: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O30" s="1" t="inlineStr">
@@ -2331,16 +2247,12 @@
         </is>
       </c>
       <c r="J31" s="1" t="inlineStr"/>
-      <c r="K31" s="1" t="inlineStr">
-        <is>
-          <t>L1016: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Get Mowatâ€™s majority down as fine as</t>
-        </is>
-      </c>
+      <c r="K31" s="1" t="inlineStr"/>
       <c r="L31" s="1" t="inlineStr"/>
       <c r="M31" s="1" t="inlineStr"/>
       <c r="N31" s="1" t="inlineStr">
         <is>
-          <t>L946: isolated marker/symbol line :: 0</t>
+          <t>L945: stray/suspicious non-ASCII glyph(s): U+4E2D CJK UNIFIED IDEOGRAPH-4E2D | isolated marker/symbol line :: 中</t>
         </is>
       </c>
       <c r="O31" s="1" t="inlineStr">
@@ -2378,14 +2290,14 @@
         </is>
       </c>
       <c r="J32" s="1" t="inlineStr"/>
-      <c r="K32" s="1" t="inlineStr">
-        <is>
-          <t>L1061: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: for the Governorship. If Mr. Singerlyâ€™s</t>
-        </is>
-      </c>
+      <c r="K32" s="1" t="inlineStr"/>
       <c r="L32" s="1" t="inlineStr"/>
       <c r="M32" s="1" t="inlineStr"/>
-      <c r="N32" s="1" t="inlineStr"/>
+      <c r="N32" s="1" t="inlineStr">
+        <is>
+          <t>L946: isolated marker/symbol line :: 0</t>
+        </is>
+      </c>
       <c r="O32" s="1" t="inlineStr">
         <is>
           <t>L1188: isolated marker/symbol line :: .</t>
@@ -2412,7 +2324,7 @@
       <c r="G33" s="1" t="inlineStr"/>
       <c r="H33" s="1" t="inlineStr">
         <is>
-          <t>L808: suspicious token(s): NormaLuxton (odd internal casing) | abbreviation/spacing may be garbled :: Leckenbyï¼ŒChas.F.A.Locke, NormaLuxton,</t>
+          <t>L808: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA | suspicious token(s): NormaLuxton (odd internal casing) | abbreviation/spacing may be garbled :: Leckenby，Chas.F.A.Locke, NormaLuxton,</t>
         </is>
       </c>
       <c r="I33" s="1" t="inlineStr">
@@ -2421,11 +2333,7 @@
         </is>
       </c>
       <c r="J33" s="1" t="inlineStr"/>
-      <c r="K33" s="1" t="inlineStr">
-        <is>
-          <t>L1087: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Whatâ€™s this we see? Sir John Thomp-</t>
-        </is>
-      </c>
+      <c r="K33" s="1" t="inlineStr"/>
       <c r="L33" s="1" t="inlineStr"/>
       <c r="M33" s="1" t="inlineStr"/>
       <c r="N33" s="1" t="inlineStr"/>
@@ -2451,7 +2359,7 @@
       <c r="G34" s="1" t="inlineStr"/>
       <c r="H34" s="1" t="inlineStr">
         <is>
-          <t>L832: suspicious token(s): MnrielHills (odd internal casing) :: vin, Fannie Gunn ï¼Œ MnrielHills ï¼› Mabel</t>
+          <t>L832: stray/suspicious non-ASCII glyph(s): U+FF0C FULLWIDTH COMMA, U+FF1B FULLWIDTH SEMICOLON | suspicious token(s): MnrielHills (odd internal casing) :: vin, Fannie Gunn ， MnrielHills ； Mabel</t>
         </is>
       </c>
       <c r="I34" s="1" t="inlineStr">
@@ -2460,11 +2368,7 @@
         </is>
       </c>
       <c r="J34" s="1" t="inlineStr"/>
-      <c r="K34" s="1" t="inlineStr">
-        <is>
-          <t>L1108: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: ning shoes at Kingsleyâ€™s, Nos. 26 and 28</t>
-        </is>
-      </c>
+      <c r="K34" s="1" t="inlineStr"/>
       <c r="L34" s="1" t="inlineStr"/>
       <c r="M34" s="1" t="inlineStr"/>
       <c r="N34" s="1" t="inlineStr"/>
@@ -2499,11 +2403,7 @@
         </is>
       </c>
       <c r="J35" s="1" t="inlineStr"/>
-      <c r="K35" s="1" t="inlineStr">
-        <is>
-          <t>L1154: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: "Are you savinâ€™ up for the Fourth of</t>
-        </is>
-      </c>
+      <c r="K35" s="1" t="inlineStr"/>
       <c r="L35" s="1" t="inlineStr"/>
       <c r="M35" s="1" t="inlineStr"/>
       <c r="N35" s="1" t="inlineStr"/>
@@ -2538,11 +2438,7 @@
         </is>
       </c>
       <c r="J36" s="1" t="inlineStr"/>
-      <c r="K36" s="1" t="inlineStr">
-        <is>
-          <t>L1160: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+2122 TRADE MARK SIGN :: Iâ€™ll have 25 cents."</t>
-        </is>
-      </c>
+      <c r="K36" s="1" t="inlineStr"/>
       <c r="L36" s="1" t="inlineStr"/>
       <c r="M36" s="1" t="inlineStr"/>
       <c r="N36" s="1" t="inlineStr"/>
@@ -2568,16 +2464,12 @@
       <c r="G37" s="1" t="inlineStr"/>
       <c r="H37" s="1" t="inlineStr">
         <is>
-          <t>L879: suspicious token(s): 25c (letter/digit mix) :: 23 and 25c, Saturday 12Â½c.</t>
+          <t>L879: suspicious token(s): 25c (letter/digit mix) :: 23 and 25c, Saturday 12½c.</t>
         </is>
       </c>
       <c r="I37" s="1" t="inlineStr"/>
       <c r="J37" s="1" t="inlineStr"/>
-      <c r="K37" s="1" t="inlineStr">
-        <is>
-          <t>L1208: stray/suspicious non-ASCII glyph(s): U+20AC EURO SIGN, U+00A2 CENT SIGN :: â€¢ up the system.</t>
-        </is>
-      </c>
+      <c r="K37" s="1" t="inlineStr"/>
       <c r="L37" s="1" t="inlineStr"/>
       <c r="M37" s="1" t="inlineStr"/>
       <c r="N37" s="1" t="inlineStr"/>
